--- a/figure3/fig3f/data/kir2.1_LH_lines.xlsx
+++ b/figure3/fig3f/data/kir2.1_LH_lines.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="w118" sheetId="1" state="visible" r:id="rId3"/>
@@ -38,7 +38,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -67,6 +67,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -76,12 +83,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -114,13 +128,21 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -247,7 +269,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -259,50 +281,82 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="2" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="2" t="n">
         <v>0.708333333333333</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>0.291666666666667</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>0.291666666666667</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="2" t="n">
         <v>0.791666666666667</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>0.416666666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>0.291666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="B7" s="0" t="n">
+      <c r="A7" s="2" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.291666666666667</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -456,7 +510,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -505,6 +559,38 @@
       </c>
       <c r="B6" s="1" t="n">
         <v>0.458333333333333</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.708333333333333</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.583333333333333</v>
       </c>
     </row>
   </sheetData>
